--- a/backend/data/financials_by_company/1237.HK.xlsx
+++ b/backend/data/financials_by_company/1237.HK.xlsx
@@ -672,596 +672,596 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>403000</v>
+        <v>1014500</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>28549000</v>
+        <v>73234000</v>
       </c>
       <c r="E2" t="n">
-        <v>1612000</v>
+        <v>4058000</v>
       </c>
       <c r="F2" t="n">
-        <v>1612000</v>
+        <v>4058000</v>
       </c>
       <c r="G2" t="n">
-        <v>2983000</v>
+        <v>48324000</v>
       </c>
       <c r="H2" t="n">
-        <v>30502000</v>
+        <v>37876000</v>
       </c>
       <c r="I2" t="n">
-        <v>359898000</v>
+        <v>486390000</v>
       </c>
       <c r="J2" t="n">
-        <v>30161000</v>
+        <v>77292000</v>
       </c>
       <c r="K2" t="n">
-        <v>-341000</v>
+        <v>39416000</v>
       </c>
       <c r="L2" t="n">
-        <v>18664000</v>
+        <v>2356000</v>
       </c>
       <c r="M2" t="n">
-        <v>3860000</v>
+        <v>1245000</v>
       </c>
       <c r="N2" t="n">
-        <v>22524000</v>
+        <v>3601000</v>
       </c>
       <c r="O2" t="n">
-        <v>1774000</v>
+        <v>45280500</v>
       </c>
       <c r="P2" t="n">
-        <v>2983000</v>
+        <v>47712000</v>
       </c>
       <c r="Q2" t="n">
-        <v>416839000</v>
+        <v>586664000</v>
       </c>
       <c r="R2" t="n">
-        <v>92137051</v>
+        <v>82454959</v>
       </c>
       <c r="S2" t="n">
-        <v>92137051</v>
+        <v>82454959</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03</v>
+        <v>0.57</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03</v>
+        <v>0.57</v>
       </c>
       <c r="V2" t="n">
-        <v>2983000</v>
+        <v>47712000</v>
       </c>
       <c r="W2" t="n">
-        <v>2983000</v>
+        <v>47712000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2983000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>47712000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-620000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>2983000</v>
+        <v>47712000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-612000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2983000</v>
+        <v>48324000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-7184000</v>
+        <v>-10153000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4201000</v>
+        <v>38171000</v>
       </c>
       <c r="AF2" t="n">
-        <v>3855000</v>
+        <v>5517000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2532000</v>
+        <v>-1804000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-2532000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+        <v>-103000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1907000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
       <c r="AL2" t="n">
-        <v>18664000</v>
+        <v>2356000</v>
       </c>
       <c r="AM2" t="n">
-        <v>3860000</v>
+        <v>1245000</v>
       </c>
       <c r="AN2" t="n">
-        <v>22524000</v>
+        <v>3601000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-7219000</v>
+        <v>21410000</v>
       </c>
       <c r="AP2" t="n">
-        <v>56941000</v>
+        <v>100274000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4549000</v>
+        <v>-2529000</v>
       </c>
       <c r="AR2" t="n">
-        <v>52815000</v>
+        <v>109015000</v>
       </c>
       <c r="AS2" t="n">
-        <v>15257000</v>
+        <v>46860000</v>
       </c>
       <c r="AT2" t="n">
-        <v>37558000</v>
+        <v>62155000</v>
       </c>
       <c r="AU2" t="n">
-        <v>49722000</v>
+        <v>121684000</v>
       </c>
       <c r="AV2" t="n">
-        <v>359898000</v>
+        <v>486390000</v>
       </c>
       <c r="AW2" t="n">
-        <v>409620000</v>
+        <v>608074000</v>
       </c>
       <c r="AX2" t="n">
-        <v>409620000</v>
+        <v>608074000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1894000</v>
+        <v>207217.835643</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.050259</v>
       </c>
       <c r="D3" t="n">
-        <v>40071000</v>
+        <v>25129000</v>
       </c>
       <c r="E3" t="n">
-        <v>-7576000</v>
+        <v>4123000</v>
       </c>
       <c r="F3" t="n">
-        <v>-7576000</v>
+        <v>4123000</v>
       </c>
       <c r="G3" t="n">
-        <v>-2364000</v>
+        <v>-6558000</v>
       </c>
       <c r="H3" t="n">
-        <v>33034000</v>
+        <v>35382000</v>
       </c>
       <c r="I3" t="n">
-        <v>277352000</v>
+        <v>411164000</v>
       </c>
       <c r="J3" t="n">
-        <v>32495000</v>
+        <v>29252000</v>
       </c>
       <c r="K3" t="n">
-        <v>-539000</v>
+        <v>-6130000</v>
       </c>
       <c r="L3" t="n">
-        <v>14835000</v>
+        <v>6804000</v>
       </c>
       <c r="M3" t="n">
-        <v>1359000</v>
+        <v>1013000</v>
       </c>
       <c r="N3" t="n">
-        <v>16194000</v>
+        <v>7817000</v>
       </c>
       <c r="O3" t="n">
-        <v>3318000</v>
+        <v>-10473782.164357</v>
       </c>
       <c r="P3" t="n">
-        <v>-2364000</v>
+        <v>-6558000</v>
       </c>
       <c r="Q3" t="n">
-        <v>321046000</v>
+        <v>483862000</v>
       </c>
       <c r="R3" t="n">
-        <v>92137051</v>
+        <v>87234989</v>
       </c>
       <c r="S3" t="n">
-        <v>92137051</v>
+        <v>87234989</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="V3" t="n">
-        <v>-2364000</v>
+        <v>-6558000</v>
       </c>
       <c r="W3" t="n">
-        <v>-2364000</v>
+        <v>-6558000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2364000</v>
+        <v>-6558000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>226000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2364000</v>
+        <v>-6784000</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2364000</v>
+        <v>-6784000</v>
       </c>
       <c r="AD3" t="n">
-        <v>466000</v>
+        <v>-359000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1898000</v>
+        <v>-7143000</v>
       </c>
       <c r="AF3" t="n">
-        <v>3336000</v>
+        <v>2206000</v>
       </c>
       <c r="AG3" t="n">
-        <v>808000</v>
+        <v>4163000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-808000</v>
+        <v>-5478000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>1315000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-4910000</v>
+      </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>14835000</v>
+        <v>6804000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1359000</v>
+        <v>1013000</v>
       </c>
       <c r="AN3" t="n">
-        <v>16194000</v>
+        <v>7817000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-23516000</v>
+        <v>-18825000</v>
       </c>
       <c r="AP3" t="n">
-        <v>43694000</v>
+        <v>72698000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1174000</v>
+        <v>-5752000</v>
       </c>
       <c r="AR3" t="n">
-        <v>46486000</v>
+        <v>83561000</v>
       </c>
       <c r="AS3" t="n">
-        <v>14650000</v>
+        <v>35533000</v>
       </c>
       <c r="AT3" t="n">
-        <v>31836000</v>
+        <v>48028000</v>
       </c>
       <c r="AU3" t="n">
-        <v>20178000</v>
+        <v>53873000</v>
       </c>
       <c r="AV3" t="n">
-        <v>277352000</v>
+        <v>411164000</v>
       </c>
       <c r="AW3" t="n">
-        <v>297530000</v>
+        <v>465037000</v>
       </c>
       <c r="AX3" t="n">
-        <v>297530000</v>
+        <v>465037000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>207217.835643</v>
+        <v>-1894000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.050259</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>25129000</v>
+        <v>40071000</v>
       </c>
       <c r="E4" t="n">
-        <v>4123000</v>
+        <v>-7576000</v>
       </c>
       <c r="F4" t="n">
-        <v>4123000</v>
+        <v>-7576000</v>
       </c>
       <c r="G4" t="n">
-        <v>-6558000</v>
+        <v>-2364000</v>
       </c>
       <c r="H4" t="n">
-        <v>35382000</v>
+        <v>33034000</v>
       </c>
       <c r="I4" t="n">
-        <v>411164000</v>
+        <v>277352000</v>
       </c>
       <c r="J4" t="n">
-        <v>29252000</v>
+        <v>32495000</v>
       </c>
       <c r="K4" t="n">
-        <v>-6130000</v>
+        <v>-539000</v>
       </c>
       <c r="L4" t="n">
-        <v>6804000</v>
+        <v>14835000</v>
       </c>
       <c r="M4" t="n">
-        <v>1013000</v>
+        <v>1359000</v>
       </c>
       <c r="N4" t="n">
-        <v>7817000</v>
+        <v>16194000</v>
       </c>
       <c r="O4" t="n">
-        <v>-10473782.164357</v>
+        <v>3318000</v>
       </c>
       <c r="P4" t="n">
-        <v>-6558000</v>
+        <v>-2364000</v>
       </c>
       <c r="Q4" t="n">
-        <v>483862000</v>
+        <v>321046000</v>
       </c>
       <c r="R4" t="n">
-        <v>87234989</v>
+        <v>92137051</v>
       </c>
       <c r="S4" t="n">
-        <v>87234989</v>
+        <v>92137051</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="V4" t="n">
-        <v>-6558000</v>
+        <v>-2364000</v>
       </c>
       <c r="W4" t="n">
-        <v>-6558000</v>
+        <v>-2364000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-6558000</v>
+        <v>-2364000</v>
       </c>
       <c r="Z4" t="n">
-        <v>226000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-6784000</v>
+        <v>-2364000</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6784000</v>
+        <v>-2364000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-359000</v>
+        <v>466000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-7143000</v>
+        <v>-1898000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2206000</v>
+        <v>3336000</v>
       </c>
       <c r="AG4" t="n">
-        <v>4163000</v>
+        <v>808000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-5478000</v>
+        <v>-808000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1315000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-4910000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>6804000</v>
+        <v>14835000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1013000</v>
+        <v>1359000</v>
       </c>
       <c r="AN4" t="n">
-        <v>7817000</v>
+        <v>16194000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-18825000</v>
+        <v>-23516000</v>
       </c>
       <c r="AP4" t="n">
-        <v>72698000</v>
+        <v>43694000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-5752000</v>
+        <v>1174000</v>
       </c>
       <c r="AR4" t="n">
-        <v>83561000</v>
+        <v>46486000</v>
       </c>
       <c r="AS4" t="n">
-        <v>35533000</v>
+        <v>14650000</v>
       </c>
       <c r="AT4" t="n">
-        <v>48028000</v>
+        <v>31836000</v>
       </c>
       <c r="AU4" t="n">
-        <v>53873000</v>
+        <v>20178000</v>
       </c>
       <c r="AV4" t="n">
-        <v>411164000</v>
+        <v>277352000</v>
       </c>
       <c r="AW4" t="n">
-        <v>465037000</v>
+        <v>297530000</v>
       </c>
       <c r="AX4" t="n">
-        <v>465037000</v>
+        <v>297530000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1014500</v>
+        <v>403000</v>
       </c>
       <c r="C5" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>73234000</v>
+        <v>28549000</v>
       </c>
       <c r="E5" t="n">
-        <v>4058000</v>
+        <v>1612000</v>
       </c>
       <c r="F5" t="n">
-        <v>4058000</v>
+        <v>1612000</v>
       </c>
       <c r="G5" t="n">
-        <v>48324000</v>
+        <v>2983000</v>
       </c>
       <c r="H5" t="n">
-        <v>37876000</v>
+        <v>30502000</v>
       </c>
       <c r="I5" t="n">
-        <v>486390000</v>
+        <v>359898000</v>
       </c>
       <c r="J5" t="n">
-        <v>77292000</v>
+        <v>30161000</v>
       </c>
       <c r="K5" t="n">
-        <v>39416000</v>
+        <v>-341000</v>
       </c>
       <c r="L5" t="n">
-        <v>2356000</v>
+        <v>18664000</v>
       </c>
       <c r="M5" t="n">
-        <v>1245000</v>
+        <v>3860000</v>
       </c>
       <c r="N5" t="n">
-        <v>3601000</v>
+        <v>22524000</v>
       </c>
       <c r="O5" t="n">
-        <v>45280500</v>
+        <v>1774000</v>
       </c>
       <c r="P5" t="n">
-        <v>47712000</v>
+        <v>2983000</v>
       </c>
       <c r="Q5" t="n">
-        <v>586664000</v>
+        <v>416839000</v>
       </c>
       <c r="R5" t="n">
-        <v>82454959</v>
+        <v>92137051</v>
       </c>
       <c r="S5" t="n">
-        <v>82454959</v>
+        <v>92137051</v>
       </c>
       <c r="T5" t="n">
-        <v>0.57</v>
+        <v>0.03</v>
       </c>
       <c r="U5" t="n">
-        <v>0.57</v>
+        <v>0.03</v>
       </c>
       <c r="V5" t="n">
-        <v>47712000</v>
+        <v>2983000</v>
       </c>
       <c r="W5" t="n">
-        <v>47712000</v>
+        <v>2983000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>47712000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-620000</v>
-      </c>
+        <v>2983000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>47712000</v>
+        <v>2983000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-612000</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>48324000</v>
+        <v>2983000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-10153000</v>
+        <v>-7184000</v>
       </c>
       <c r="AE5" t="n">
-        <v>38171000</v>
+        <v>-4201000</v>
       </c>
       <c r="AF5" t="n">
-        <v>5517000</v>
+        <v>3855000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1804000</v>
+        <v>2532000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-103000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1907000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
+        <v>-2532000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>2356000</v>
+        <v>18664000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1245000</v>
+        <v>3860000</v>
       </c>
       <c r="AN5" t="n">
-        <v>3601000</v>
+        <v>22524000</v>
       </c>
       <c r="AO5" t="n">
-        <v>21410000</v>
+        <v>-7219000</v>
       </c>
       <c r="AP5" t="n">
-        <v>100274000</v>
+        <v>56941000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-2529000</v>
+        <v>4549000</v>
       </c>
       <c r="AR5" t="n">
-        <v>109015000</v>
+        <v>52815000</v>
       </c>
       <c r="AS5" t="n">
-        <v>46860000</v>
+        <v>15257000</v>
       </c>
       <c r="AT5" t="n">
-        <v>62155000</v>
+        <v>37558000</v>
       </c>
       <c r="AU5" t="n">
-        <v>121684000</v>
+        <v>49722000</v>
       </c>
       <c r="AV5" t="n">
-        <v>486390000</v>
+        <v>359898000</v>
       </c>
       <c r="AW5" t="n">
-        <v>608074000</v>
+        <v>409620000</v>
       </c>
       <c r="AX5" t="n">
-        <v>608074000</v>
+        <v>409620000</v>
       </c>
     </row>
   </sheetData>
@@ -1617,199 +1617,207 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>92137000</v>
+        <v>85036800</v>
       </c>
       <c r="C2" t="n">
-        <v>92137000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>159200000</v>
-      </c>
+        <v>85036800</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>186400000</v>
+        <v>58427000</v>
       </c>
       <c r="F2" t="n">
-        <v>874856000</v>
+        <v>869872000</v>
       </c>
       <c r="G2" t="n">
-        <v>1061256000</v>
+        <v>928248000</v>
       </c>
       <c r="H2" t="n">
-        <v>550746000</v>
+        <v>417721000</v>
       </c>
       <c r="I2" t="n">
-        <v>874856000</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>869872000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>51000</v>
+      </c>
       <c r="K2" t="n">
-        <v>874856000</v>
+        <v>869872000</v>
       </c>
       <c r="L2" t="n">
-        <v>994856000</v>
+        <v>869872000</v>
       </c>
       <c r="M2" t="n">
-        <v>874856000</v>
+        <v>875392000</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5520000</v>
       </c>
       <c r="O2" t="n">
-        <v>874856000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>60236000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>695243000</v>
-      </c>
+        <v>869872000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>38462000</v>
+        <v>35345000</v>
       </c>
       <c r="S2" t="n">
-        <v>38462000</v>
+        <v>35345000</v>
       </c>
       <c r="T2" t="n">
-        <v>335972000</v>
+        <v>113983000</v>
       </c>
       <c r="U2" t="n">
-        <v>128489000</v>
+        <v>7440000</v>
       </c>
       <c r="V2" t="n">
-        <v>3610000</v>
+        <v>4680000</v>
       </c>
       <c r="W2" t="n">
-        <v>4879000</v>
+        <v>2760000</v>
       </c>
       <c r="X2" t="n">
-        <v>120000000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="n">
-        <v>120000000</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>207483000</v>
+        <v>106543000</v>
       </c>
       <c r="AB2" t="n">
-        <v>66400000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>58427000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>51000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>66400000</v>
+        <v>58376000</v>
       </c>
       <c r="AE2" t="n">
         <v>390000</v>
       </c>
       <c r="AF2" t="n">
-        <v>114632000</v>
+        <v>27790000</v>
       </c>
       <c r="AG2" t="n">
-        <v>25438000</v>
+        <v>8716000</v>
       </c>
       <c r="AH2" t="n">
-        <v>3885000</v>
+        <v>11649000</v>
       </c>
       <c r="AI2" t="n">
-        <v>85309000</v>
+        <v>7425000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1210828000</v>
+        <v>989375000</v>
       </c>
       <c r="AK2" t="n">
-        <v>452599000</v>
+        <v>465111000</v>
       </c>
       <c r="AL2" t="n">
-        <v>3772000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>1213000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>30000000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>88252000</v>
+        <v>32342000</v>
       </c>
       <c r="AO2" t="n">
-        <v>88252000</v>
+        <v>32342000</v>
       </c>
       <c r="AP2" t="n">
-        <v>29509000</v>
+        <v>30358000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>323590000</v>
+        <v>401198000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-473231000</v>
+        <v>-384940000</v>
       </c>
       <c r="AS2" t="n">
-        <v>796821000</v>
+        <v>786138000</v>
       </c>
       <c r="AT2" t="n">
-        <v>649000</v>
+        <v>1698000</v>
       </c>
       <c r="AU2" t="n">
-        <v>82442000</v>
+        <v>83359000</v>
       </c>
       <c r="AV2" t="n">
-        <v>188225000</v>
+        <v>175475000</v>
       </c>
       <c r="AW2" t="n">
-        <v>525505000</v>
+        <v>525606000</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>758229000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>524264000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2250000</v>
+      </c>
       <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>5077000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
       <c r="BC2" t="n">
-        <v>168613000</v>
+        <v>1640000</v>
       </c>
       <c r="BD2" t="n">
-        <v>65496000</v>
+        <v>130284000</v>
       </c>
       <c r="BE2" t="n">
-        <v>123652000</v>
+        <v>133547000</v>
       </c>
       <c r="BF2" t="n">
-        <v>28334000</v>
+        <v>33398000</v>
       </c>
       <c r="BG2" t="n">
-        <v>57211000</v>
+        <v>20340000</v>
       </c>
       <c r="BH2" t="n">
-        <v>38107000</v>
+        <v>79809000</v>
       </c>
       <c r="BI2" t="n">
-        <v>14191000</v>
+        <v>1961000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>77394000</v>
+        <v>97242000</v>
       </c>
       <c r="BK2" t="n">
-        <v>-17909000</v>
+        <v>-17938000</v>
       </c>
       <c r="BL2" t="n">
-        <v>95303000</v>
+        <v>115180000</v>
       </c>
       <c r="BM2" t="n">
-        <v>308883000</v>
+        <v>154513000</v>
       </c>
       <c r="BN2" t="n">
-        <v>281683000</v>
+        <v>92842000</v>
       </c>
       <c r="BO2" t="n">
-        <v>27200000</v>
-      </c>
-      <c r="BP2" t="inlineStr"/>
+        <v>61671000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>61671000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>92137000</v>
@@ -1817,44 +1825,42 @@
       <c r="C3" t="n">
         <v>92137000</v>
       </c>
-      <c r="D3" t="n">
-        <v>54401000</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>86900000</v>
+        <v>54019000</v>
       </c>
       <c r="F3" t="n">
-        <v>872372000</v>
+        <v>879493000</v>
       </c>
       <c r="G3" t="n">
-        <v>959272000</v>
+        <v>933443000</v>
       </c>
       <c r="H3" t="n">
-        <v>349910000</v>
+        <v>433073000</v>
       </c>
       <c r="I3" t="n">
-        <v>872372000</v>
+        <v>879493000</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="K3" t="n">
-        <v>872372000</v>
+        <v>879493000</v>
       </c>
       <c r="L3" t="n">
-        <v>882372000</v>
+        <v>879493000</v>
       </c>
       <c r="M3" t="n">
-        <v>872372000</v>
+        <v>880377000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>884000</v>
       </c>
       <c r="O3" t="n">
-        <v>872372000</v>
+        <v>879493000</v>
       </c>
       <c r="P3" t="n">
-        <v>57253000</v>
+        <v>60423000</v>
       </c>
       <c r="Q3" t="n">
         <v>695243000</v>
@@ -1866,87 +1872,89 @@
         <v>38462000</v>
       </c>
       <c r="T3" t="n">
-        <v>182369000</v>
+        <v>136214000</v>
       </c>
       <c r="U3" t="n">
-        <v>17170000</v>
+        <v>6694000</v>
       </c>
       <c r="V3" t="n">
-        <v>3900000</v>
+        <v>4290000</v>
       </c>
       <c r="W3" t="n">
-        <v>3270000</v>
+        <v>2404000</v>
       </c>
       <c r="X3" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>165199000</v>
+        <v>129520000</v>
       </c>
       <c r="AB3" t="n">
-        <v>76900000</v>
+        <v>54019000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="AD3" t="n">
-        <v>76900000</v>
+        <v>53950000</v>
       </c>
       <c r="AE3" t="n">
         <v>390000</v>
       </c>
       <c r="AF3" t="n">
-        <v>69851000</v>
+        <v>50663000</v>
       </c>
       <c r="AG3" t="n">
-        <v>25359000</v>
+        <v>20513000</v>
       </c>
       <c r="AH3" t="n">
-        <v>11987000</v>
+        <v>11619000</v>
       </c>
       <c r="AI3" t="n">
-        <v>32505000</v>
+        <v>18531000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1054741000</v>
+        <v>1016591000</v>
       </c>
       <c r="AK3" t="n">
-        <v>539632000</v>
+        <v>453998000</v>
       </c>
       <c r="AL3" t="n">
-        <v>3193000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>1378000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>47000000</v>
+      </c>
       <c r="AN3" t="n">
-        <v>163776000</v>
+        <v>50945000</v>
       </c>
       <c r="AO3" t="n">
-        <v>163776000</v>
+        <v>50945000</v>
       </c>
       <c r="AP3" t="n">
-        <v>31222000</v>
+        <v>32936000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>341441000</v>
+        <v>368739000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-447639000</v>
+        <v>-417526000</v>
       </c>
       <c r="AS3" t="n">
-        <v>789080000</v>
+        <v>786265000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2665000</v>
+        <v>220000</v>
       </c>
       <c r="AU3" t="n">
-        <v>82442000</v>
+        <v>82564000</v>
       </c>
       <c r="AV3" t="n">
-        <v>178367000</v>
+        <v>177875000</v>
       </c>
       <c r="AW3" t="n">
         <v>525606000</v>
@@ -1955,59 +1963,61 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>515109000</v>
+        <v>562593000</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>771000</v>
+        <v>42000</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>856000</v>
       </c>
       <c r="BC3" t="n">
-        <v>77051000</v>
+        <v>53578000</v>
       </c>
       <c r="BD3" t="n">
-        <v>55467000</v>
+        <v>66846000</v>
       </c>
       <c r="BE3" t="n">
-        <v>115940000</v>
+        <v>89874000</v>
       </c>
       <c r="BF3" t="n">
-        <v>31677000</v>
+        <v>10004000</v>
       </c>
       <c r="BG3" t="n">
-        <v>21413000</v>
+        <v>18334000</v>
       </c>
       <c r="BH3" t="n">
-        <v>62850000</v>
+        <v>61536000</v>
       </c>
       <c r="BI3" t="n">
-        <v>8924000</v>
+        <v>69000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>48821000</v>
+        <v>122955000</v>
       </c>
       <c r="BK3" t="n">
-        <v>-13360000</v>
+        <v>-12186000</v>
       </c>
       <c r="BL3" t="n">
-        <v>62181000</v>
+        <v>64665000</v>
       </c>
       <c r="BM3" t="n">
-        <v>208135000</v>
+        <v>295219000</v>
       </c>
       <c r="BN3" t="n">
-        <v>175636000</v>
+        <v>181454000</v>
       </c>
       <c r="BO3" t="n">
-        <v>32499000</v>
-      </c>
-      <c r="BP3" t="inlineStr"/>
+        <v>113765000</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>113765000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>92137000</v>
@@ -2015,42 +2025,44 @@
       <c r="C4" t="n">
         <v>92137000</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>54401000</v>
+      </c>
       <c r="E4" t="n">
-        <v>54019000</v>
+        <v>86900000</v>
       </c>
       <c r="F4" t="n">
-        <v>879493000</v>
+        <v>872372000</v>
       </c>
       <c r="G4" t="n">
-        <v>933443000</v>
+        <v>959272000</v>
       </c>
       <c r="H4" t="n">
-        <v>433073000</v>
+        <v>349910000</v>
       </c>
       <c r="I4" t="n">
-        <v>879493000</v>
+        <v>872372000</v>
       </c>
       <c r="J4" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>879493000</v>
+        <v>872372000</v>
       </c>
       <c r="L4" t="n">
-        <v>879493000</v>
+        <v>882372000</v>
       </c>
       <c r="M4" t="n">
-        <v>880377000</v>
+        <v>872372000</v>
       </c>
       <c r="N4" t="n">
-        <v>884000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>879493000</v>
+        <v>872372000</v>
       </c>
       <c r="P4" t="n">
-        <v>60423000</v>
+        <v>57253000</v>
       </c>
       <c r="Q4" t="n">
         <v>695243000</v>
@@ -2062,89 +2074,87 @@
         <v>38462000</v>
       </c>
       <c r="T4" t="n">
-        <v>136214000</v>
+        <v>182369000</v>
       </c>
       <c r="U4" t="n">
-        <v>6694000</v>
+        <v>17170000</v>
       </c>
       <c r="V4" t="n">
-        <v>4290000</v>
+        <v>3900000</v>
       </c>
       <c r="W4" t="n">
-        <v>2404000</v>
+        <v>3270000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>129520000</v>
+        <v>165199000</v>
       </c>
       <c r="AB4" t="n">
-        <v>54019000</v>
+        <v>76900000</v>
       </c>
       <c r="AC4" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>53950000</v>
+        <v>76900000</v>
       </c>
       <c r="AE4" t="n">
         <v>390000</v>
       </c>
       <c r="AF4" t="n">
-        <v>50663000</v>
+        <v>69851000</v>
       </c>
       <c r="AG4" t="n">
-        <v>20513000</v>
+        <v>25359000</v>
       </c>
       <c r="AH4" t="n">
-        <v>11619000</v>
+        <v>11987000</v>
       </c>
       <c r="AI4" t="n">
-        <v>18531000</v>
+        <v>32505000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1016591000</v>
+        <v>1054741000</v>
       </c>
       <c r="AK4" t="n">
-        <v>453998000</v>
+        <v>539632000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1378000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>47000000</v>
-      </c>
+        <v>3193000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>50945000</v>
+        <v>163776000</v>
       </c>
       <c r="AO4" t="n">
-        <v>50945000</v>
+        <v>163776000</v>
       </c>
       <c r="AP4" t="n">
-        <v>32936000</v>
+        <v>31222000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>368739000</v>
+        <v>341441000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-417526000</v>
+        <v>-447639000</v>
       </c>
       <c r="AS4" t="n">
-        <v>786265000</v>
+        <v>789080000</v>
       </c>
       <c r="AT4" t="n">
-        <v>220000</v>
+        <v>2665000</v>
       </c>
       <c r="AU4" t="n">
-        <v>82564000</v>
+        <v>82442000</v>
       </c>
       <c r="AV4" t="n">
-        <v>177875000</v>
+        <v>178367000</v>
       </c>
       <c r="AW4" t="n">
         <v>525606000</v>
@@ -2153,257 +2163,247 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>562593000</v>
+        <v>515109000</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>42000</v>
+        <v>771000</v>
       </c>
       <c r="BB4" t="n">
-        <v>856000</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>53578000</v>
+        <v>77051000</v>
       </c>
       <c r="BD4" t="n">
-        <v>66846000</v>
+        <v>55467000</v>
       </c>
       <c r="BE4" t="n">
-        <v>89874000</v>
+        <v>115940000</v>
       </c>
       <c r="BF4" t="n">
-        <v>10004000</v>
+        <v>31677000</v>
       </c>
       <c r="BG4" t="n">
-        <v>18334000</v>
+        <v>21413000</v>
       </c>
       <c r="BH4" t="n">
-        <v>61536000</v>
+        <v>62850000</v>
       </c>
       <c r="BI4" t="n">
-        <v>69000</v>
+        <v>8924000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>122955000</v>
+        <v>48821000</v>
       </c>
       <c r="BK4" t="n">
-        <v>-12186000</v>
+        <v>-13360000</v>
       </c>
       <c r="BL4" t="n">
-        <v>64665000</v>
+        <v>62181000</v>
       </c>
       <c r="BM4" t="n">
-        <v>295219000</v>
+        <v>208135000</v>
       </c>
       <c r="BN4" t="n">
-        <v>181454000</v>
+        <v>175636000</v>
       </c>
       <c r="BO4" t="n">
-        <v>113765000</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>113765000</v>
-      </c>
+        <v>32499000</v>
+      </c>
+      <c r="BP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>85036800</v>
+        <v>92137000</v>
       </c>
       <c r="C5" t="n">
-        <v>85036800</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>92137000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>159200000</v>
+      </c>
       <c r="E5" t="n">
-        <v>58427000</v>
+        <v>186400000</v>
       </c>
       <c r="F5" t="n">
-        <v>869872000</v>
+        <v>874856000</v>
       </c>
       <c r="G5" t="n">
-        <v>928248000</v>
+        <v>1061256000</v>
       </c>
       <c r="H5" t="n">
-        <v>417721000</v>
+        <v>550746000</v>
       </c>
       <c r="I5" t="n">
-        <v>869872000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>51000</v>
-      </c>
+        <v>874856000</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>869872000</v>
+        <v>874856000</v>
       </c>
       <c r="L5" t="n">
-        <v>869872000</v>
+        <v>994856000</v>
       </c>
       <c r="M5" t="n">
-        <v>875392000</v>
+        <v>874856000</v>
       </c>
       <c r="N5" t="n">
-        <v>5520000</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>869872000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>874856000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>60236000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>695243000</v>
+      </c>
       <c r="R5" t="n">
-        <v>35345000</v>
+        <v>38462000</v>
       </c>
       <c r="S5" t="n">
-        <v>35345000</v>
+        <v>38462000</v>
       </c>
       <c r="T5" t="n">
-        <v>113983000</v>
+        <v>335972000</v>
       </c>
       <c r="U5" t="n">
-        <v>7440000</v>
+        <v>128489000</v>
       </c>
       <c r="V5" t="n">
-        <v>4680000</v>
+        <v>3610000</v>
       </c>
       <c r="W5" t="n">
-        <v>2760000</v>
+        <v>4879000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
+        <v>120000000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>106543000</v>
+        <v>207483000</v>
       </c>
       <c r="AB5" t="n">
-        <v>58427000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>51000</v>
-      </c>
+        <v>66400000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>58376000</v>
+        <v>66400000</v>
       </c>
       <c r="AE5" t="n">
         <v>390000</v>
       </c>
       <c r="AF5" t="n">
-        <v>27790000</v>
+        <v>114632000</v>
       </c>
       <c r="AG5" t="n">
-        <v>8716000</v>
+        <v>25438000</v>
       </c>
       <c r="AH5" t="n">
-        <v>11649000</v>
+        <v>3885000</v>
       </c>
       <c r="AI5" t="n">
-        <v>7425000</v>
+        <v>85309000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>989375000</v>
+        <v>1210828000</v>
       </c>
       <c r="AK5" t="n">
-        <v>465111000</v>
+        <v>452599000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1213000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>30000000</v>
-      </c>
+        <v>3772000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>32342000</v>
+        <v>88252000</v>
       </c>
       <c r="AO5" t="n">
-        <v>32342000</v>
+        <v>88252000</v>
       </c>
       <c r="AP5" t="n">
-        <v>30358000</v>
+        <v>29509000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>401198000</v>
+        <v>323590000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-384940000</v>
+        <v>-473231000</v>
       </c>
       <c r="AS5" t="n">
-        <v>786138000</v>
+        <v>796821000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1698000</v>
+        <v>649000</v>
       </c>
       <c r="AU5" t="n">
-        <v>83359000</v>
+        <v>82442000</v>
       </c>
       <c r="AV5" t="n">
-        <v>175475000</v>
+        <v>188225000</v>
       </c>
       <c r="AW5" t="n">
-        <v>525606000</v>
+        <v>525505000</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>524264000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2250000</v>
-      </c>
+        <v>758229000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>5077000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>1640000</v>
+        <v>168613000</v>
       </c>
       <c r="BD5" t="n">
-        <v>130284000</v>
+        <v>65496000</v>
       </c>
       <c r="BE5" t="n">
-        <v>133547000</v>
+        <v>123652000</v>
       </c>
       <c r="BF5" t="n">
-        <v>33398000</v>
+        <v>28334000</v>
       </c>
       <c r="BG5" t="n">
-        <v>20340000</v>
+        <v>57211000</v>
       </c>
       <c r="BH5" t="n">
-        <v>79809000</v>
+        <v>38107000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1961000</v>
+        <v>14191000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>97242000</v>
+        <v>77394000</v>
       </c>
       <c r="BK5" t="n">
-        <v>-17938000</v>
+        <v>-17909000</v>
       </c>
       <c r="BL5" t="n">
-        <v>115180000</v>
+        <v>95303000</v>
       </c>
       <c r="BM5" t="n">
-        <v>154513000</v>
+        <v>308883000</v>
       </c>
       <c r="BN5" t="n">
-        <v>92842000</v>
+        <v>281683000</v>
       </c>
       <c r="BO5" t="n">
-        <v>61671000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>61671000</v>
-      </c>
+        <v>27200000</v>
+      </c>
+      <c r="BP5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2673,578 +2673,578 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>22327000</v>
+        <v>-49080000</v>
       </c>
       <c r="C2" t="n">
-        <v>-132400000</v>
+        <v>-20129000</v>
       </c>
       <c r="D2" t="n">
-        <v>231900000</v>
+        <v>74407000</v>
       </c>
       <c r="E2" t="n">
-        <v>-11144000</v>
+        <v>-13203000</v>
       </c>
       <c r="F2" t="n">
-        <v>27200000</v>
+        <v>61671000</v>
       </c>
       <c r="G2" t="n">
-        <v>32499000</v>
+        <v>137969000</v>
       </c>
       <c r="H2" t="n">
-        <v>-2883000</v>
+        <v>7885000</v>
       </c>
       <c r="I2" t="n">
-        <v>-2416000</v>
+        <v>-84183000</v>
       </c>
       <c r="J2" t="n">
-        <v>96432000</v>
+        <v>57914000</v>
       </c>
       <c r="K2" t="n">
-        <v>792000</v>
+        <v>4898000</v>
       </c>
       <c r="L2" t="n">
-        <v>-3860000</v>
+        <v>-1235000</v>
       </c>
       <c r="M2" t="n">
-        <v>99500000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>54278000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>54278000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-20129000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>74407000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>99500000</v>
+        <v>54278000</v>
       </c>
       <c r="R2" t="n">
-        <v>-132400000</v>
+        <v>-20129000</v>
       </c>
       <c r="S2" t="n">
-        <v>231900000</v>
+        <v>74407000</v>
       </c>
       <c r="T2" t="n">
-        <v>-132319000</v>
+        <v>-106220000</v>
       </c>
       <c r="U2" t="n">
-        <v>-99038000</v>
+        <v>2950000</v>
       </c>
       <c r="V2" t="n">
-        <v>7157000</v>
+        <v>2953000</v>
       </c>
       <c r="W2" t="n">
-        <v>709000</v>
+        <v>195000</v>
       </c>
       <c r="X2" t="n">
-        <v>-30213000</v>
+        <v>-92443000</v>
       </c>
       <c r="Y2" t="n">
-        <v>176009000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-206222000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+        <v>-92443000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-4611000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-4611000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>-10934000</v>
+        <v>-12764000</v>
       </c>
       <c r="AF2" t="n">
-        <v>210000</v>
+        <v>439000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-11144000</v>
+        <v>-13203000</v>
       </c>
       <c r="AH2" t="n">
-        <v>33471000</v>
+        <v>-35877000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-30000</v>
+        <v>7000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21108000</v>
+        <v>-110343000</v>
       </c>
       <c r="AK2" t="n">
-        <v>5001000</v>
+        <v>3779000</v>
       </c>
       <c r="AL2" t="n">
-        <v>61113000</v>
+        <v>-831000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-7712000</v>
+        <v>-18413000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-37294000</v>
+        <v>-94878000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-18664000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>-2356000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7706000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>4549000</v>
+        <v>-2529000</v>
       </c>
       <c r="AR2" t="n">
-        <v>30502000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>37876000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1476000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>30502000</v>
+        <v>37876000</v>
       </c>
       <c r="AU2" t="n">
-        <v>211000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>-5601000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
       <c r="AW2" t="n">
-        <v>-4000</v>
+        <v>-103000</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>-4201000</v>
+        <v>37559000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>20331000</v>
+        <v>197795000</v>
       </c>
       <c r="C3" t="n">
-        <v>-53950000</v>
+        <v>-54000000</v>
       </c>
       <c r="D3" t="n">
-        <v>86900000</v>
+        <v>53950000</v>
       </c>
       <c r="E3" t="n">
-        <v>-4078000</v>
+        <v>-7195000</v>
       </c>
       <c r="F3" t="n">
-        <v>32499000</v>
+        <v>113914000</v>
       </c>
       <c r="G3" t="n">
-        <v>113914000</v>
+        <v>61671000</v>
       </c>
       <c r="H3" t="n">
-        <v>1103000</v>
+        <v>8243000</v>
       </c>
       <c r="I3" t="n">
-        <v>-82518000</v>
+        <v>44000000</v>
       </c>
       <c r="J3" t="n">
-        <v>36801000</v>
+        <v>-547000</v>
       </c>
       <c r="K3" t="n">
-        <v>5279000</v>
+        <v>526000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1331000</v>
+        <v>-918000</v>
       </c>
       <c r="M3" t="n">
-        <v>32950000</v>
+        <v>-50000</v>
       </c>
       <c r="N3" t="n">
-        <v>32950000</v>
+        <v>-50000</v>
       </c>
       <c r="O3" t="n">
-        <v>-53950000</v>
+        <v>-54000000</v>
       </c>
       <c r="P3" t="n">
-        <v>86900000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>32950000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-53950000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>86900000</v>
-      </c>
+        <v>53950000</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>-143728000</v>
+        <v>-160443000</v>
       </c>
       <c r="U3" t="n">
-        <v>-23473000</v>
+        <v>-51938000</v>
       </c>
       <c r="V3" t="n">
-        <v>6091000</v>
+        <v>2938000</v>
       </c>
       <c r="W3" t="n">
-        <v>727000</v>
+        <v>177000</v>
       </c>
       <c r="X3" t="n">
-        <v>-123022000</v>
+        <v>-108600000</v>
       </c>
       <c r="Y3" t="n">
-        <v>203925000</v>
+        <v>101572000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-326947000</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+        <v>-210172000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-4051000</v>
+        <v>-4810000</v>
       </c>
       <c r="AF3" t="n">
-        <v>27000</v>
+        <v>2385000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4078000</v>
+        <v>-7195000</v>
       </c>
       <c r="AH3" t="n">
-        <v>24409000</v>
+        <v>204990000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-25000</v>
+        <v>-59000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110000</v>
+        <v>186198000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-5918000</v>
+        <v>4122000</v>
       </c>
       <c r="AL3" t="n">
-        <v>13408000</v>
+        <v>22756000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-26066000</v>
+        <v>43673000</v>
       </c>
       <c r="AN3" t="n">
-        <v>18686000</v>
+        <v>115647000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-14835000</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>-11714000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>1174000</v>
+        <v>-5752000</v>
       </c>
       <c r="AR3" t="n">
-        <v>33034000</v>
+        <v>35382000</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>33034000</v>
+        <v>35382000</v>
       </c>
       <c r="AU3" t="n">
-        <v>7657000</v>
+        <v>-137000</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>4605000</v>
       </c>
       <c r="AW3" t="n">
-        <v>30000</v>
+        <v>-568000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-838000</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>-1898000</v>
+        <v>-7143000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>197795000</v>
+        <v>20331000</v>
       </c>
       <c r="C4" t="n">
-        <v>-54000000</v>
+        <v>-53950000</v>
       </c>
       <c r="D4" t="n">
-        <v>53950000</v>
+        <v>86900000</v>
       </c>
       <c r="E4" t="n">
-        <v>-7195000</v>
+        <v>-4078000</v>
       </c>
       <c r="F4" t="n">
+        <v>32499000</v>
+      </c>
+      <c r="G4" t="n">
         <v>113914000</v>
       </c>
-      <c r="G4" t="n">
-        <v>61671000</v>
-      </c>
       <c r="H4" t="n">
-        <v>8243000</v>
+        <v>1103000</v>
       </c>
       <c r="I4" t="n">
-        <v>44000000</v>
+        <v>-82518000</v>
       </c>
       <c r="J4" t="n">
-        <v>-547000</v>
+        <v>36801000</v>
       </c>
       <c r="K4" t="n">
-        <v>526000</v>
+        <v>5279000</v>
       </c>
       <c r="L4" t="n">
-        <v>-918000</v>
+        <v>-1331000</v>
       </c>
       <c r="M4" t="n">
-        <v>-50000</v>
+        <v>32950000</v>
       </c>
       <c r="N4" t="n">
-        <v>-50000</v>
+        <v>32950000</v>
       </c>
       <c r="O4" t="n">
-        <v>-54000000</v>
+        <v>-53950000</v>
       </c>
       <c r="P4" t="n">
-        <v>53950000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+        <v>86900000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>32950000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-53950000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>86900000</v>
+      </c>
       <c r="T4" t="n">
-        <v>-160443000</v>
+        <v>-143728000</v>
       </c>
       <c r="U4" t="n">
-        <v>-51938000</v>
+        <v>-23473000</v>
       </c>
       <c r="V4" t="n">
-        <v>2938000</v>
+        <v>6091000</v>
       </c>
       <c r="W4" t="n">
-        <v>177000</v>
+        <v>727000</v>
       </c>
       <c r="X4" t="n">
-        <v>-108600000</v>
+        <v>-123022000</v>
       </c>
       <c r="Y4" t="n">
-        <v>101572000</v>
+        <v>203925000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-210172000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>-326947000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-4810000</v>
+        <v>-4051000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2385000</v>
+        <v>27000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-7195000</v>
+        <v>-4078000</v>
       </c>
       <c r="AH4" t="n">
-        <v>204990000</v>
+        <v>24409000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-59000</v>
+        <v>-25000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>186198000</v>
+        <v>110000</v>
       </c>
       <c r="AK4" t="n">
-        <v>4122000</v>
+        <v>-5918000</v>
       </c>
       <c r="AL4" t="n">
-        <v>22756000</v>
+        <v>13408000</v>
       </c>
       <c r="AM4" t="n">
-        <v>43673000</v>
+        <v>-26066000</v>
       </c>
       <c r="AN4" t="n">
-        <v>115647000</v>
+        <v>18686000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-11714000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
+        <v>-14835000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>-5752000</v>
+        <v>1174000</v>
       </c>
       <c r="AR4" t="n">
-        <v>35382000</v>
+        <v>33034000</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>35382000</v>
+        <v>33034000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-137000</v>
+        <v>7657000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4605000</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-568000</v>
+        <v>30000</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>-838000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-7143000</v>
+        <v>-1898000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-49080000</v>
+        <v>22327000</v>
       </c>
       <c r="C5" t="n">
-        <v>-20129000</v>
+        <v>-132400000</v>
       </c>
       <c r="D5" t="n">
-        <v>74407000</v>
+        <v>231900000</v>
       </c>
       <c r="E5" t="n">
-        <v>-13203000</v>
+        <v>-11144000</v>
       </c>
       <c r="F5" t="n">
-        <v>61671000</v>
+        <v>27200000</v>
       </c>
       <c r="G5" t="n">
-        <v>137969000</v>
+        <v>32499000</v>
       </c>
       <c r="H5" t="n">
-        <v>7885000</v>
+        <v>-2883000</v>
       </c>
       <c r="I5" t="n">
-        <v>-84183000</v>
+        <v>-2416000</v>
       </c>
       <c r="J5" t="n">
-        <v>57914000</v>
+        <v>96432000</v>
       </c>
       <c r="K5" t="n">
-        <v>4898000</v>
+        <v>792000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1235000</v>
+        <v>-3860000</v>
       </c>
       <c r="M5" t="n">
-        <v>54278000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>54278000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-20129000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>74407000</v>
-      </c>
+        <v>99500000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>54278000</v>
+        <v>99500000</v>
       </c>
       <c r="R5" t="n">
-        <v>-20129000</v>
+        <v>-132400000</v>
       </c>
       <c r="S5" t="n">
-        <v>74407000</v>
+        <v>231900000</v>
       </c>
       <c r="T5" t="n">
-        <v>-106220000</v>
+        <v>-132319000</v>
       </c>
       <c r="U5" t="n">
-        <v>2950000</v>
+        <v>-99038000</v>
       </c>
       <c r="V5" t="n">
-        <v>2953000</v>
+        <v>7157000</v>
       </c>
       <c r="W5" t="n">
-        <v>195000</v>
+        <v>709000</v>
       </c>
       <c r="X5" t="n">
-        <v>-92443000</v>
+        <v>-30213000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>176009000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-92443000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-4611000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-4611000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+        <v>-206222000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-12764000</v>
+        <v>-10934000</v>
       </c>
       <c r="AF5" t="n">
-        <v>439000</v>
+        <v>210000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-13203000</v>
+        <v>-11144000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-35877000</v>
+        <v>33471000</v>
       </c>
       <c r="AI5" t="n">
-        <v>7000</v>
+        <v>-30000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-110343000</v>
+        <v>21108000</v>
       </c>
       <c r="AK5" t="n">
-        <v>3779000</v>
+        <v>5001000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-831000</v>
+        <v>61113000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-18413000</v>
+        <v>-7712000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-94878000</v>
+        <v>-37294000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-2356000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>7706000</v>
-      </c>
+        <v>-18664000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>-2529000</v>
+        <v>4549000</v>
       </c>
       <c r="AR5" t="n">
-        <v>37876000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1476000</v>
-      </c>
+        <v>30502000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>37876000</v>
+        <v>30502000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-5601000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
+        <v>211000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>-103000</v>
+        <v>-4000</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>37559000</v>
+        <v>-4201000</v>
       </c>
     </row>
   </sheetData>
@@ -3784,187 +3784,187 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>China Environmental Technology and Bioenergy Holdings Limited, an investment holding company, manufactures and sells outdoor wooden products in the People's Republic of China, Australasia, North America, Europe, and the Asia Pacific. It operates in two segments, Manufacturing and Sales of Wooden Products; and Manufacturing and Sales of Renewable Energy Products. The company offers timber villas for leisure resort clubs, tourist scenic spots, and parks; non-residential timber sheds for leisure or storage purposes, including pavilions and gazebos, etc.; timber logs which are processed with drying, coating, polishing, and anti-corrosive treatment; and timber houses, and related parts and structures, as well as provides installation advice services. It also provides recreational products, such as play swings, sand tables, and outdoor rocking chairs for children, public parks and private gardens, and courtyards; tables and chairs for outdoors usage; indoor furniture products, including beds and cabinets; landscape garden products comprising flower carts, railings, and litter bins for use in gardens, scenic spots, courtyards, and parks; and pet-home products, including bird houses, dog homes and playhouses, rabbit hutches, hamster cages, etc. In addition, the company trades in timber; and recycles, produces, and sells biomass pellet fuels. The company was formerly known as Merry Garden Holdings Limited and changed its name to China Environmental Technology and Bioenergy Holdings Limited in June 2016. China Environmental Technology and Bioenergy Holdings Limited was founded in 1995 and is headquartered in Zhangping, China.</t>
+          <t>China Environmental Technology and Bioenergy Holdings Limited, an investment holding company, manufactures and sells outdoor wooden products in the People's Republic of China, Australia, North America, Europe, and the Asia Pacific. It operates in two segments, Manufacturing and Sales of Wooden Products; and Manufacturing and Sales of Renewable Energy Products. The company offers timber villas for leisure resort clubs, tourist scenic spots, and parks; non-residential timber sheds for leisure or storage purposes, including pavilions and gazebos, etc.; timber logs which are processed with drying, coating, polishing, and/or anti-corrosive treatment; and timber houses, and related parts and structures, as well as provides installation advice services. It also provides recreational products, such as play swings, sand tables, and outdoor rocking chairs for children, public parks and private gardens, and courtyards; tables and chairs for outdoors usage; indoor furniture products, including beds and cabinets; landscape garden products, comprising flower carts, railings, and litter bins for use in gardens, scenic spots, courtyards, and parks; and pet-home products, including bird houses, dog homes, and playhouses, rabbit hutches, hamster cages, etc. In addition, the company trades in timber; and recycles, produces, and sells biomass pellet fuels. The company was formerly known as Merry Garden Holdings Limited and changed its name to China Environmental Technology and Bioenergy Holdings Limited in June 2016. China Environmental Technology and Bioenergy Holdings Limited was founded in 1995 and is headquartered in Zhangping, China.</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Qingmei  Xie', 'age': 57, 'title': 'Executive Chairlady of the Board', 'yearBorn': 1968, 'fiscalYear': 2025, 'totalPay': 359117, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zheyan  Wu', 'age': 46, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1979, 'fiscalYear': 2025, 'totalPay': 3351371, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tianfu  Chen', 'age': 59, 'title': 'Chief Financial Officer', 'yearBorn': 1966, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Lun  Wong CPA, FCPA, Hkicpa', 'age': 41, 'title': 'Company Secretary', 'yearBorn': 1984, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Qingmei  Xie', 'age': 57, 'title': 'Executive Chairlady of the Board', 'yearBorn': 1968, 'fiscalYear': 2025, 'totalPay': 358831, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zheyan  Wu', 'age': 46, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1979, 'fiscalYear': 2025, 'totalPay': 3348700, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tianfu  Chen', 'age': 59, 'title': 'Chief Financial Officer', 'yearBorn': 1966, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Lun  Wong CPA, FCPA, Hkicpa', 'age': 41, 'title': 'Company Secretary', 'yearBorn': 1984, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -4052,28 +4052,28 @@
         <v>3</v>
       </c>
       <c r="R2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="S2" t="n">
         <v>0.72</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.73</v>
       </c>
       <c r="T2" t="n">
         <v>0.72</v>
       </c>
       <c r="U2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.73</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>0.72</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.73</v>
       </c>
       <c r="X2" t="n">
         <v>0.72</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="Z2" t="n">
         <v>1431561600</v>
@@ -4082,31 +4082,31 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.673</v>
+        <v>0.678</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.2857144</v>
+        <v>1.3214285</v>
       </c>
       <c r="AD2" t="n">
-        <v>73492</v>
+        <v>70000</v>
       </c>
       <c r="AE2" t="n">
-        <v>73492</v>
+        <v>70000</v>
       </c>
       <c r="AF2" t="n">
-        <v>63717</v>
+        <v>72694</v>
       </c>
       <c r="AG2" t="n">
-        <v>86460</v>
+        <v>59701</v>
       </c>
       <c r="AH2" t="n">
-        <v>86460</v>
+        <v>59701</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>69146680</v>
+        <v>71067416</v>
       </c>
       <c r="AN2" t="n">
-        <v>69146676</v>
+        <v>70107047</v>
       </c>
       <c r="AO2" t="n">
         <v>0.355</v>
@@ -4133,13 +4133,13 @@
         <v>0.26</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.14419107</v>
+        <v>0.14819637</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.7638</v>
+        <v>0.7866</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.83275</v>
+        <v>0.8097</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4156,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>136321632</v>
+        <v>138242384</v>
       </c>
       <c r="BA2" t="n">
         <v>0.093210004</v>
@@ -4177,10 +4177,10 @@
         <v>96037051</v>
       </c>
       <c r="BG2" t="n">
-        <v>11.0573225</v>
+        <v>11.048511</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.06511522</v>
+        <v>0.06697735</v>
       </c>
       <c r="BI2" t="n">
         <v>1767139200</v>
@@ -4209,16 +4209,16 @@
         <v>1704153600</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.284</v>
+        <v>0.288</v>
       </c>
       <c r="BR2" t="n">
-        <v>6.176</v>
+        <v>6.263</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.8947368999999999</v>
+        <v>0.89610386</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>0.227264</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -4334,137 +4334,137 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="n">
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>CH ENV TECH&amp;BIO</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>China Environmental Technology and Bioenergy Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.046599984</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0.05924229</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.0697</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.08608127</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1781768954</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>finmb_211947980</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>1.3698617</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
         <v>1341538200000</v>
       </c>
-      <c r="DC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>0.72 - 0.73</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.00999999</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>0.72 - 0.72</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DF2" t="n">
-        <v>63717</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.36500004</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>1.0281692</v>
-      </c>
-      <c r="DI2" t="inlineStr">
+      <c r="EB2" t="n">
+        <v>72694</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.38500002</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1.0845071</v>
+      </c>
+      <c r="EE2" t="inlineStr">
         <is>
           <t>0.355 - 1.5</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>89.47369</v>
-      </c>
-      <c r="DM2" t="n">
+      <c r="EF2" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.50666666</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>89.61038000000001</v>
+      </c>
+      <c r="EI2" t="n">
         <v>1743424195</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="EJ2" t="n">
         <v>1743424195</v>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.043799996</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.057344846</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.112749994</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.13539477</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>1780386922</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>CH ENV TECH&amp;BIO</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>China Environmental Technology and Bioenergy Holdings Limited</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>finmb_211947980</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
       </c>
       <c r="EK2" t="b">
         <v>0</v>
